--- a/htr-FHIR/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
